--- a/schools-presentations/A Gymnasiou/kahoot/A5.2 Μ1 - Διαχείριση Ηλεκτρονικού Ταχυδρομείου.xlsx
+++ b/schools-presentations/A Gymnasiou/kahoot/A5.2 Μ1 - Διαχείριση Ηλεκτρονικού Ταχυδρομείου.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kahoot Quiz" sheetId="1" r:id="R252e8f912e4d43b2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kahoot Quiz" sheetId="1" r:id="Rfb340d91791a4539"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -55,7 +55,7 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFFFF4CC"/>
+        <x:fgColor rgb="FFFFF1C7"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -340,30 +340,30 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="38" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="31" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="31" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="31" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="31" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="42" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="34" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="34" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="34" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="34" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="16" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="18" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="42" customHeight="1">
       <x:c r="A1" s="6" t="str">
-        <x:v>Question - max 95 characters</x:v>
+        <x:v>Question - max 120 characters</x:v>
       </x:c>
       <x:c r="B1" s="6" t="str">
-        <x:v>Answer 1 - max 60 characters</x:v>
+        <x:v>Answer 1 - max 75 characters</x:v>
       </x:c>
       <x:c r="C1" s="6" t="str">
-        <x:v>Answer 2 - max 60 characters</x:v>
+        <x:v>Answer 2 - max 75 characters</x:v>
       </x:c>
       <x:c r="D1" s="6" t="str">
-        <x:v>Answer 3 - max 60 characters</x:v>
+        <x:v>Answer 3 - max 75 characters</x:v>
       </x:c>
       <x:c r="E1" s="6" t="str">
-        <x:v>Answer 4 - max 60 characters</x:v>
+        <x:v>Answer 4 - max 75 characters</x:v>
       </x:c>
       <x:c r="F1" s="6" t="str">
         <x:v>Time limit (sec)</x:v>
@@ -372,53 +372,53 @@
         <x:v>Correct answer(s)</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" ht="58" customHeight="1">
+    <x:row r="2" ht="62" customHeight="1">
       <x:c r="A2" s="11" t="str">
-        <x:v>Σε ποιον φάκελο βρίσκονται τα μηνύματα που έχουμε παραλάβει;</x:v>
+        <x:v>Σε ποιον φάκελο εμφανίζονται τα μηνύματα που μόλις λάβαμε;</x:v>
       </x:c>
       <x:c r="B2" s="11" t="str">
-        <x:v>Στα Εισερχόμενα (Inbox)</x:v>
+        <x:v>Πρόχειρα (Drafts)</x:v>
       </x:c>
       <x:c r="C2" s="11" t="str">
-        <x:v>Στα Απεσταλμένα (Sent)</x:v>
+        <x:v>Εισερχόμενα (Inbox)</x:v>
       </x:c>
       <x:c r="D2" s="11" t="str">
-        <x:v>Στα Πρόχειρα (Drafts)</x:v>
+        <x:v>Απεσταλμένα (Sent)</x:v>
       </x:c>
       <x:c r="E2" s="11" t="str">
-        <x:v>Στα Εξερχόμενα (Outbox)</x:v>
+        <x:v>Εξερχόμενα (Outbox)</x:v>
       </x:c>
       <x:c r="F2" s="14" t="n">
         <x:v>20</x:v>
       </x:c>
       <x:c r="G2" s="14" t="str">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" ht="58" customHeight="1">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="62" customHeight="1">
       <x:c r="A3" s="11" t="str">
-        <x:v>Σε ποιον φάκελο βρίσκονται τα μηνύματα που έχουν αποσταλεί;</x:v>
+        <x:v>Πού βρίσκουμε ένα μήνυμα που έχει ήδη αποσταλεί επιτυχώς;</x:v>
       </x:c>
       <x:c r="B3" s="11" t="str">
-        <x:v>Στα Εισερχόμενα (Inbox)</x:v>
+        <x:v>Εξερχόμενα (Outbox)</x:v>
       </x:c>
       <x:c r="C3" s="11" t="str">
-        <x:v>Στα Απεσταλμένα (Sent)</x:v>
+        <x:v>Εισερχόμενα (Inbox)</x:v>
       </x:c>
       <x:c r="D3" s="11" t="str">
-        <x:v>Στα Εξερχόμενα (Outbox)</x:v>
+        <x:v>Πρόχειρα (Drafts)</x:v>
       </x:c>
       <x:c r="E3" s="11" t="str">
-        <x:v>Στον Κάδο (Trash)</x:v>
+        <x:v>Απεσταλμένα (Sent)</x:v>
       </x:c>
       <x:c r="F3" s="14" t="n">
         <x:v>20</x:v>
       </x:c>
       <x:c r="G3" s="14" t="str">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" ht="58" customHeight="1">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="62" customHeight="1">
       <x:c r="A4" s="11" t="str">
         <x:v>Τι περιέχει συνήθως ο φάκελος Εξερχόμενα (Outbox);</x:v>
       </x:c>
@@ -426,13 +426,13 @@
         <x:v>Μηνύματα που περιμένουν να αποσταλούν</x:v>
       </x:c>
       <x:c r="C4" s="11" t="str">
-        <x:v>Μηνύματα που έχουμε παραλάβει</x:v>
+        <x:v>Μηνύματα που λάβαμε και δεν διαβάσαμε</x:v>
       </x:c>
       <x:c r="D4" s="11" t="str">
-        <x:v>Επαφές από το βιβλίο διευθύνσεων</x:v>
+        <x:v>Μηνύματα που αποθηκεύσαμε ως πρόχειρα</x:v>
       </x:c>
       <x:c r="E4" s="11" t="str">
-        <x:v>Μηνύματα που έχουμε διαγράψει</x:v>
+        <x:v>Μηνύματα που διαγράψαμε πρόσφατα</x:v>
       </x:c>
       <x:c r="F4" s="14" t="n">
         <x:v>30</x:v>
@@ -441,44 +441,44 @@
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="5" ht="58" customHeight="1">
+    <x:row r="5" ht="62" customHeight="1">
       <x:c r="A5" s="11" t="str">
-        <x:v>Τι κάνει η εντολή Reply;</x:v>
+        <x:v>Ποια εντολή απαντά μόνο στον αποστολέα του μηνύματος;</x:v>
       </x:c>
       <x:c r="B5" s="11" t="str">
-        <x:v>Απαντά μόνο στον αρχικό αποστολέα</x:v>
+        <x:v>Forward</x:v>
       </x:c>
       <x:c r="C5" s="11" t="str">
-        <x:v>Απαντά σε όλους τους παραλήπτες</x:v>
+        <x:v>Reply all</x:v>
       </x:c>
       <x:c r="D5" s="11" t="str">
-        <x:v>Προωθεί το μήνυμα σε νέο άτομο</x:v>
+        <x:v>Reply</x:v>
       </x:c>
       <x:c r="E5" s="11" t="str">
-        <x:v>Διαγράφει το μήνυμα</x:v>
+        <x:v>New message</x:v>
       </x:c>
       <x:c r="F5" s="14" t="n">
         <x:v>20</x:v>
       </x:c>
       <x:c r="G5" s="14" t="str">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="58" customHeight="1">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="62" customHeight="1">
       <x:c r="A6" s="11" t="str">
         <x:v>Τι κάνει η εντολή Reply all;</x:v>
       </x:c>
       <x:c r="B6" s="11" t="str">
-        <x:v>Απαντά μόνο στον αποστολέα</x:v>
+        <x:v>Προωθεί το μήνυμα σε νέα άτομα</x:v>
       </x:c>
       <x:c r="C6" s="11" t="str">
         <x:v>Απαντά στον αποστολέα και στους άλλους παραλήπτες</x:v>
       </x:c>
       <x:c r="D6" s="11" t="str">
-        <x:v>Αποθηκεύει το μήνυμα στα Πρόχειρα</x:v>
+        <x:v>Απαντά μόνο στον αποστολέα</x:v>
       </x:c>
       <x:c r="E6" s="11" t="str">
-        <x:v>Στέλνει το μήνυμα μόνο στον εαυτό μας</x:v>
+        <x:v>Αποθηκεύει την απάντηση στα Πρόχειρα</x:v>
       </x:c>
       <x:c r="F6" s="14" t="n">
         <x:v>30</x:v>
@@ -487,119 +487,119 @@
         <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="7" ht="58" customHeight="1">
+    <x:row r="7" ht="62" customHeight="1">
       <x:c r="A7" s="11" t="str">
-        <x:v>Τι μπορούμε να κάνουμε στο Βιβλίο Διευθύνσεων;</x:v>
+        <x:v>Ποια εργασία γίνεται στο Βιβλίο Διευθύνσεων;</x:v>
       </x:c>
       <x:c r="B7" s="11" t="str">
-        <x:v>Να προσθέτουμε, να διαγράφουμε και να ομαδοποιούμε επαφές</x:v>
+        <x:v>Μεταφορά μηνυμάτων στα Απεσταλμένα</x:v>
       </x:c>
       <x:c r="C7" s="11" t="str">
-        <x:v>Να αποθηκεύουμε μόνο επισυναπτόμενα αρχεία</x:v>
+        <x:v>Έλεγχος της ταχύτητας σύνδεσης</x:v>
       </x:c>
       <x:c r="D7" s="11" t="str">
-        <x:v>Να αλλάζουμε τη σύνδεση στο Διαδίκτυο</x:v>
+        <x:v>Δημιουργία φίλτρων για κάθε μήνυμα</x:v>
       </x:c>
       <x:c r="E7" s="11" t="str">
-        <x:v>Να διαγράφουμε τον λογαριασμό e-mail</x:v>
+        <x:v>Προσθήκη και ομαδοποίηση επαφών</x:v>
       </x:c>
       <x:c r="F7" s="14" t="n">
         <x:v>30</x:v>
       </x:c>
       <x:c r="G7" s="14" t="str">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="58" customHeight="1">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="62" customHeight="1">
       <x:c r="A8" s="11" t="str">
-        <x:v>Μπορεί το ίδιο μήνυμα να σταλεί σε πολλά άτομα;</x:v>
+        <x:v>Πώς στέλνουμε το ίδιο μήνυμα σε περισσότερα από ένα άτομα;</x:v>
       </x:c>
       <x:c r="B8" s="11" t="str">
-        <x:v>Ναι, μπορεί να έχει πολλούς παραλήπτες</x:v>
+        <x:v>Προσθέτουμε περισσότερες διευθύνσεις παραληπτών</x:v>
       </x:c>
       <x:c r="C8" s="11" t="str">
-        <x:v>Όχι, κάθε μήνυμα έχει μόνο έναν παραλήπτη</x:v>
+        <x:v>Δημιουργούμε διαφορετικό λογαριασμό για κάθε άτομο</x:v>
       </x:c>
       <x:c r="D8" s="11" t="str">
-        <x:v>Μόνο αν δεν έχει θέμα</x:v>
+        <x:v>Μεταφέρουμε πρώτα το μήνυμα στα Πρόχειρα</x:v>
       </x:c>
       <x:c r="E8" s="11" t="str">
-        <x:v>Μόνο αν όλοι έχουν τον ίδιο παροχέα</x:v>
+        <x:v>Γράφουμε τις διευθύνσεις μέσα στο θέμα</x:v>
       </x:c>
       <x:c r="F8" s="14" t="n">
-        <x:v>20</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="G8" s="14" t="str">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" ht="58" customHeight="1">
+    <x:row r="9" ht="62" customHeight="1">
       <x:c r="A9" s="11" t="str">
-        <x:v>Τι πρέπει να κάνουμε σε κοινόχρηστο υπολογιστή μετά τη χρήση e-mail;</x:v>
+        <x:v>Τι είναι σημαντικό σε κοινόχρηστο υπολογιστή μετά τη χρήση e-mail;</x:v>
       </x:c>
       <x:c r="B9" s="11" t="str">
+        <x:v>Να αφήσουμε ανοικτά μόνο τα Εισερχόμενα</x:v>
+      </x:c>
+      <x:c r="C9" s="11" t="str">
+        <x:v>Να διαγράψουμε όλες τις επαφές μας</x:v>
+      </x:c>
+      <x:c r="D9" s="11" t="str">
         <x:v>Να αποσυνδεθούμε από τον λογαριασμό</x:v>
       </x:c>
-      <x:c r="C9" s="11" t="str">
-        <x:v>Να αφήσουμε τον λογαριασμό ανοικτό</x:v>
-      </x:c>
-      <x:c r="D9" s="11" t="str">
-        <x:v>Να διαγράψουμε όλες τις επαφές</x:v>
-      </x:c>
       <x:c r="E9" s="11" t="str">
-        <x:v>Να κλείσουμε μόνο ένα μήνυμα</x:v>
+        <x:v>Να μεταφέρουμε τα μηνύματα στον Κάδο</x:v>
       </x:c>
       <x:c r="F9" s="14" t="n">
         <x:v>30</x:v>
       </x:c>
       <x:c r="G9" s="14" t="str">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" ht="58" customHeight="1">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="62" customHeight="1">
       <x:c r="A10" s="13" t="str">
-        <x:v>Μήνυμα στάλθηκε σε εσένα και δύο συμμαθητές. Θέλεις να απαντήσεις σε όλους. Τι πατάς;</x:v>
+        <x:v>Μήνυμα ήρθε σε εσένα και τρεις συμμαθητές. Θέλεις να απαντήσεις σε όλους. Τι επιλέγεις;</x:v>
       </x:c>
       <x:c r="B10" s="12" t="str">
-        <x:v>Reply</x:v>
+        <x:v>Forward προς τους τρεις συμμαθητές</x:v>
       </x:c>
       <x:c r="C10" s="12" t="str">
-        <x:v>Reply all</x:v>
+        <x:v>Reply και προσθήκη των διευθύνσεων στο κείμενο</x:v>
       </x:c>
       <x:c r="D10" s="12" t="str">
-        <x:v>Delete</x:v>
+        <x:v>New message μόνο προς τον αποστολέα</x:v>
       </x:c>
       <x:c r="E10" s="12" t="str">
-        <x:v>New message</x:v>
+        <x:v>Reply all, αφού ελέγξεις ποιοι θα λάβουν την απάντηση</x:v>
       </x:c>
       <x:c r="F10" s="15" t="n">
         <x:v>60</x:v>
       </x:c>
       <x:c r="G10" s="15" t="str">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" ht="58" customHeight="1">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="62" customHeight="1">
       <x:c r="A11" s="13" t="str">
-        <x:v>Ένα μήνυμα είναι στο Outbox και μετά αποστέλλεται. Πού θα εμφανιστεί;</x:v>
+        <x:v>Μήνυμα βρίσκεται στο Outbox και η σύνδεση επανέρχεται. Ποια εξέλιξη είναι πιθανότερη;</x:v>
       </x:c>
       <x:c r="B11" s="12" t="str">
-        <x:v>Στα Εισερχόμενα</x:v>
+        <x:v>Παραμένει για πάντα στο Outbox</x:v>
       </x:c>
       <x:c r="C11" s="12" t="str">
-        <x:v>Στα Πρόχειρα</x:v>
+        <x:v>Αποστέλλεται και εμφανίζεται στα Sent</x:v>
       </x:c>
       <x:c r="D11" s="12" t="str">
-        <x:v>Στα Απεσταλμένα</x:v>
+        <x:v>Μεταφέρεται αυτόματα στα Drafts</x:v>
       </x:c>
       <x:c r="E11" s="12" t="str">
-        <x:v>Στο Βιβλίο Διευθύνσεων</x:v>
+        <x:v>Εμφανίζεται ως νέο μήνυμα στο Inbox</x:v>
       </x:c>
       <x:c r="F11" s="15" t="n">
         <x:v>60</x:v>
       </x:c>
       <x:c r="G11" s="15" t="str">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
